--- a/Alkem Lab DCF Model.xlsx
+++ b/Alkem Lab DCF Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anuj8\Downloads\Jobaaj Data\Alkem Laboratories Annual Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anuj8\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C945B38-3EAD-4252-8DC4-419B5CA0BB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC4324C-54DF-4FB4-B87A-435A2BC8D54E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9DA9CA1D-8B62-4D2D-A7DF-257820A61D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9DA9CA1D-8B62-4D2D-A7DF-257820A61D34}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="458">
   <si>
     <t>Heading</t>
   </si>
@@ -1494,6 +1494,12 @@
   </si>
   <si>
     <t>Exit Multiple</t>
+  </si>
+  <si>
+    <t>Change in Working Capital</t>
+  </si>
+  <si>
+    <t>Less: Capex</t>
   </si>
 </sst>
 </file>
@@ -2919,7 +2925,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Profit &amp; Loss"/>
@@ -7227,7 +7232,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B94D503-F6B2-482D-AD79-DC25781CBA8D}">
-  <dimension ref="A1:S189"/>
+  <dimension ref="A1:S188"/>
   <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="1.33203125" style="1" customWidth="1"/>
@@ -11970,8 +11975,8 @@
         <v>432</v>
       </c>
       <c r="R142" s="147">
-        <f>M153*(1+E132)/(E133-E132)</f>
-        <v>617812.33907397662</v>
+        <f>M152*(1+E132)/(E133-E132)</f>
+        <v>624624.45132091409</v>
       </c>
     </row>
     <row r="143" spans="4:18" x14ac:dyDescent="0.3">
@@ -12007,7 +12012,7 @@
       <c r="Q143" s="4"/>
       <c r="R143" s="149">
         <f>AVERAGE(R141:R142)</f>
-        <v>725310.5704831616</v>
+        <v>728716.62660663039</v>
       </c>
     </row>
     <row r="145" spans="4:14" x14ac:dyDescent="0.3">
@@ -12122,317 +12127,299 @@
       </c>
     </row>
     <row r="150" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D150" t="str" cm="1">
-        <f t="array" ref="D150:D152">D78:D80</f>
-        <v>(+/-) Non Cash Expenses</v>
+      <c r="D150" t="s">
+        <v>457</v>
       </c>
       <c r="I150" s="39">
-        <f>M78</f>
-        <v>813.8530485648904</v>
+        <f>-M114</f>
+        <v>-2976.9670632621142</v>
       </c>
       <c r="J150" s="39">
-        <f t="shared" ref="J150:M150" si="33">N78</f>
-        <v>813.8530485648904</v>
+        <f t="shared" ref="J150:M150" si="33">-N114</f>
+        <v>-2914.4507549336049</v>
       </c>
       <c r="K150" s="39">
         <f t="shared" si="33"/>
-        <v>813.8530485648904</v>
+        <v>-2824.7148161892028</v>
       </c>
       <c r="L150" s="39">
         <f t="shared" si="33"/>
-        <v>813.8530485648904</v>
+        <v>-2713.1298243338006</v>
       </c>
       <c r="M150" s="39">
         <f t="shared" si="33"/>
-        <v>813.8530485648904</v>
+        <v>-2584.9133889597183</v>
       </c>
     </row>
     <row r="151" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D151" t="str">
-        <v>(+/-) Non Operating Losses</v>
+      <c r="D151" t="s">
+        <v>456</v>
       </c>
       <c r="I151" s="39">
-        <f>M79</f>
-        <v>-2733.4857514339501</v>
-      </c>
-      <c r="J151" s="39">
-        <f t="shared" ref="J151:M151" si="34">N79</f>
-        <v>-2976.7659833115713</v>
-      </c>
-      <c r="K151" s="39">
-        <f t="shared" si="34"/>
-        <v>-3212.555616849681</v>
-      </c>
-      <c r="L151" s="39">
-        <f t="shared" si="34"/>
-        <v>-3439.0308289151712</v>
-      </c>
-      <c r="M151" s="39">
-        <f t="shared" si="34"/>
-        <v>-3654.8033299893964</v>
-      </c>
-    </row>
-    <row r="152" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D152" t="str">
-        <v>(+/-) Change In Working Capital</v>
-      </c>
-      <c r="I152" s="39">
         <f>M80</f>
         <v>-6551.9694252958725</v>
       </c>
-      <c r="J152" s="39">
-        <f t="shared" ref="J152:M152" si="35">N80</f>
+      <c r="J151" s="39">
+        <f>N80</f>
         <v>-3742.0111788513386</v>
       </c>
-      <c r="K152" s="39">
-        <f t="shared" si="35"/>
+      <c r="K151" s="39">
+        <f>O80</f>
         <v>-3626.7946546544954</v>
       </c>
-      <c r="L152" s="39">
-        <f t="shared" si="35"/>
+      <c r="L151" s="39">
+        <f>P80</f>
         <v>-3483.525022732214</v>
       </c>
-      <c r="M152" s="39">
-        <f t="shared" si="35"/>
+      <c r="M151" s="39">
+        <f>Q80</f>
         <v>-3318.9014367374693</v>
       </c>
     </row>
-    <row r="153" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D153" s="41" t="s">
+    <row r="152" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D152" s="41" t="s">
         <v>429</v>
       </c>
-      <c r="E153" s="26"/>
-      <c r="F153" s="26"/>
-      <c r="G153" s="26"/>
-      <c r="H153" s="26"/>
-      <c r="I153" s="144">
-        <f>SUM(I148:I152)</f>
-        <v>13649.253467983966</v>
-      </c>
-      <c r="J153" s="144">
-        <f t="shared" ref="J153:M153" si="36">SUM(J148:J152)</f>
-        <v>18133.850691196694</v>
-      </c>
-      <c r="K153" s="144">
-        <f t="shared" si="36"/>
-        <v>19871.870692797194</v>
-      </c>
-      <c r="L153" s="144">
-        <f t="shared" si="36"/>
-        <v>21573.056706504998</v>
-      </c>
-      <c r="M153" s="144">
-        <f t="shared" si="36"/>
-        <v>23220.808126585885</v>
-      </c>
-      <c r="N153" s="148">
+      <c r="E152" s="26"/>
+      <c r="F152" s="26"/>
+      <c r="G152" s="26"/>
+      <c r="H152" s="26"/>
+      <c r="I152" s="144">
+        <f>SUM(I148:I151)</f>
+        <v>12591.919107590911</v>
+      </c>
+      <c r="J152" s="144">
+        <f>SUM(J148:J151)</f>
+        <v>17382.31287100977</v>
+      </c>
+      <c r="K152" s="144">
+        <f>SUM(K148:K151)</f>
+        <v>19445.85844489278</v>
+      </c>
+      <c r="L152" s="144">
+        <f>SUM(L148:L151)</f>
+        <v>21485.104662521477</v>
+      </c>
+      <c r="M152" s="144">
+        <f>SUM(M148:M151)</f>
+        <v>23476.845019050674</v>
+      </c>
+      <c r="N152" s="148">
         <f>R143</f>
-        <v>725310.5704831616</v>
-      </c>
-    </row>
-    <row r="155" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D155" t="s">
+        <v>728716.62660663039</v>
+      </c>
+    </row>
+    <row r="154" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D154" t="s">
         <v>430</v>
       </c>
-      <c r="H155">
+      <c r="H154">
         <v>0</v>
       </c>
-      <c r="I155">
-        <f>I153*I143</f>
-        <v>1327.0107538317745</v>
-      </c>
-      <c r="J155">
-        <f t="shared" ref="J155:N155" si="37">J153*J143</f>
-        <v>18133.850691196694</v>
-      </c>
-      <c r="K155">
-        <f t="shared" si="37"/>
-        <v>19871.870692797194</v>
-      </c>
-      <c r="L155">
-        <f t="shared" si="37"/>
-        <v>21573.056706504998</v>
-      </c>
-      <c r="M155">
-        <f t="shared" si="37"/>
-        <v>23220.808126585885</v>
-      </c>
-      <c r="N155">
-        <f t="shared" si="37"/>
-        <v>725310.5704831616</v>
-      </c>
+      <c r="I154">
+        <f>I152*I143</f>
+        <v>1224.2143576824496</v>
+      </c>
+      <c r="J154">
+        <f>J152*J143</f>
+        <v>17382.31287100977</v>
+      </c>
+      <c r="K154">
+        <f>K152*K143</f>
+        <v>19445.85844489278</v>
+      </c>
+      <c r="L154">
+        <f>L152*L143</f>
+        <v>21485.104662521477</v>
+      </c>
+      <c r="M154">
+        <f>M152*M143</f>
+        <v>23476.845019050674</v>
+      </c>
+      <c r="N154">
+        <f>N152*N143</f>
+        <v>728716.62660663039</v>
+      </c>
+    </row>
+    <row r="158" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D158" s="106" t="s">
+        <v>436</v>
+      </c>
+      <c r="E158" s="142"/>
+      <c r="H158" s="106" t="s">
+        <v>444</v>
+      </c>
+      <c r="I158" s="142"/>
+      <c r="J158" s="142"/>
+      <c r="L158" s="106" t="s">
+        <v>449</v>
+      </c>
+      <c r="M158" s="142"/>
+      <c r="N158" s="142"/>
     </row>
     <row r="159" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D159" s="106" t="s">
-        <v>436</v>
-      </c>
-      <c r="E159" s="142"/>
-      <c r="H159" s="106" t="s">
-        <v>444</v>
-      </c>
-      <c r="I159" s="142"/>
-      <c r="J159" s="142"/>
-      <c r="L159" s="106" t="s">
-        <v>449</v>
-      </c>
-      <c r="M159" s="142"/>
-      <c r="N159" s="142"/>
+      <c r="D159" t="s">
+        <v>437</v>
+      </c>
+      <c r="E159" s="86">
+        <f>XNPV(E133,H154:N154,H141:N141)</f>
+        <v>558342.24115968368</v>
+      </c>
+      <c r="H159" t="s">
+        <v>292</v>
+      </c>
+      <c r="J159" s="86">
+        <f>Comps_Data!F9</f>
+        <v>688613.20000000007</v>
+      </c>
+      <c r="L159" t="s">
+        <v>450</v>
+      </c>
+      <c r="M159" s="86">
+        <f>J165</f>
+        <v>5757.635451505017</v>
+      </c>
     </row>
     <row r="160" spans="4:14" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
-        <v>437</v>
-      </c>
-      <c r="E160" s="86">
-        <f>XNPV(E133,H155:N155,H141:N141)</f>
-        <v>557055.5923210769</v>
+        <v>438</v>
+      </c>
+      <c r="E160" s="39">
+        <f>L44+L45+L53</f>
+        <v>61430.899999999994</v>
       </c>
       <c r="H160" t="s">
-        <v>292</v>
-      </c>
-      <c r="J160" s="86">
-        <f>Comps_Data!F9</f>
-        <v>688613.20000000007</v>
+        <v>445</v>
+      </c>
+      <c r="J160" s="39">
+        <f>-E161</f>
+        <v>13809</v>
       </c>
       <c r="L160" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M160" s="86">
-        <f>J166</f>
-        <v>5757.635451505017</v>
+        <f>E165</f>
+        <v>5029.0680698970209</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="D161" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E161" s="39">
-        <f>L44+L45+L53</f>
-        <v>61430.899999999994</v>
+        <f>-L121</f>
+        <v>-13809</v>
       </c>
       <c r="H161" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J161" s="39">
         <f>-E162</f>
-        <v>13809</v>
+        <v>4487.6000000000004</v>
       </c>
       <c r="L161" t="s">
-        <v>451</v>
-      </c>
-      <c r="M161" s="86">
-        <f>E166</f>
-        <v>5018.3101364638533</v>
+        <v>452</v>
+      </c>
+      <c r="M161" s="56">
+        <f>M160/M159-1</f>
+        <v>-0.12653933854349053</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E162" s="39">
-        <f>-L121</f>
-        <v>-13809</v>
+        <f>-L69</f>
+        <v>-4487.6000000000004</v>
       </c>
       <c r="H162" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J162" s="39">
-        <f>-E163</f>
-        <v>4487.6000000000004</v>
-      </c>
-      <c r="L162" t="s">
-        <v>452</v>
-      </c>
-      <c r="M162" s="56">
-        <f>M161/M160-1</f>
-        <v>-0.12840780234669213</v>
-      </c>
+        <f>-E160</f>
+        <v>-61430.899999999994</v>
+      </c>
+      <c r="M162" s="56"/>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="D163" t="s">
-        <v>440</v>
-      </c>
-      <c r="E163" s="39">
-        <f>-L69</f>
-        <v>-4487.6000000000004</v>
+        <v>322</v>
+      </c>
+      <c r="E163" s="146">
+        <f>SUM(E159:E162)</f>
+        <v>601476.54115968372</v>
       </c>
       <c r="H163" t="s">
-        <v>447</v>
-      </c>
-      <c r="J163" s="39">
-        <f>-E161</f>
-        <v>-61430.899999999994</v>
-      </c>
-      <c r="M163" s="56"/>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="D164" t="s">
-        <v>322</v>
-      </c>
-      <c r="E164" s="146">
-        <f>SUM(E160:E163)</f>
-        <v>600189.89232107694</v>
-      </c>
-      <c r="H164" t="s">
         <v>448</v>
       </c>
-      <c r="J164" s="86">
-        <f>SUM(J160:J163)</f>
+      <c r="J163" s="86">
+        <f>SUM(J159:J162)</f>
         <v>645478.9</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="D166" t="s">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D165" t="s">
         <v>443</v>
       </c>
-      <c r="E166">
-        <f>E164/E134</f>
-        <v>5018.3101364638533</v>
-      </c>
-      <c r="H166" t="s">
+      <c r="E165">
+        <f>E163/E134</f>
+        <v>5029.0680698970209</v>
+      </c>
+      <c r="H165" t="s">
         <v>443</v>
       </c>
-      <c r="J166" s="86">
-        <f>J160/E134</f>
+      <c r="J165" s="86">
+        <f>J159/E134</f>
         <v>5757.635451505017</v>
       </c>
     </row>
-    <row r="169" spans="1:17" ht="21" x14ac:dyDescent="0.4">
-      <c r="A169" s="35" t="s">
+    <row r="168" spans="1:17" ht="21" x14ac:dyDescent="0.4">
+      <c r="A168" s="35" t="s">
         <v>453</v>
       </c>
-      <c r="B169" s="36"/>
-      <c r="C169" s="36"/>
-      <c r="D169" s="37"/>
-      <c r="E169" s="37"/>
-      <c r="F169" s="37"/>
-      <c r="G169" s="37"/>
-      <c r="H169" s="37"/>
-      <c r="I169" s="37"/>
-      <c r="J169" s="37"/>
-      <c r="K169" s="37"/>
-      <c r="L169" s="37"/>
-      <c r="M169" s="37"/>
-      <c r="N169" s="37"/>
-      <c r="O169" s="37"/>
-      <c r="P169" s="37"/>
-      <c r="Q169" s="37"/>
-    </row>
-    <row r="171" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B168" s="36"/>
+      <c r="C168" s="36"/>
+      <c r="D168" s="37"/>
+      <c r="E168" s="37"/>
+      <c r="F168" s="37"/>
+      <c r="G168" s="37"/>
+      <c r="H168" s="37"/>
+      <c r="I168" s="37"/>
+      <c r="J168" s="37"/>
+      <c r="K168" s="37"/>
+      <c r="L168" s="37"/>
+      <c r="M168" s="37"/>
+      <c r="N168" s="37"/>
+      <c r="O168" s="37"/>
+      <c r="P168" s="37"/>
+      <c r="Q168" s="37"/>
+    </row>
+    <row r="170" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A170" s="157"/>
+      <c r="B170" s="157"/>
+      <c r="C170" s="157"/>
+      <c r="D170" s="158"/>
+      <c r="E170" s="158"/>
+      <c r="F170" s="158"/>
+      <c r="H170" s="150" t="s">
+        <v>454</v>
+      </c>
+      <c r="I170" s="150"/>
+      <c r="J170" s="150"/>
+      <c r="K170" s="150"/>
+      <c r="L170" s="150"/>
+      <c r="M170" s="150"/>
+      <c r="N170" s="150"/>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" s="157"/>
       <c r="B171" s="157"/>
       <c r="C171" s="157"/>
       <c r="D171" s="158"/>
       <c r="E171" s="158"/>
       <c r="F171" s="158"/>
-      <c r="H171" s="150" t="s">
-        <v>454</v>
-      </c>
-      <c r="I171" s="150"/>
-      <c r="J171" s="150"/>
-      <c r="K171" s="150"/>
-      <c r="L171" s="150"/>
-      <c r="M171" s="150"/>
-      <c r="N171" s="150"/>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" s="157"/>
@@ -12441,6 +12428,13 @@
       <c r="D172" s="158"/>
       <c r="E172" s="158"/>
       <c r="F172" s="158"/>
+      <c r="J172" s="152" t="s">
+        <v>455</v>
+      </c>
+      <c r="K172" s="151"/>
+      <c r="L172" s="151"/>
+      <c r="M172" s="151"/>
+      <c r="N172" s="151"/>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" s="157"/>
@@ -12449,13 +12443,25 @@
       <c r="D173" s="158"/>
       <c r="E173" s="158"/>
       <c r="F173" s="158"/>
-      <c r="J173" s="152" t="s">
-        <v>455</v>
-      </c>
-      <c r="K173" s="151"/>
-      <c r="L173" s="151"/>
-      <c r="M173" s="151"/>
-      <c r="N173" s="151"/>
+      <c r="I173" s="156">
+        <f>E165</f>
+        <v>5029.0680698970209</v>
+      </c>
+      <c r="J173" s="154">
+        <v>15</v>
+      </c>
+      <c r="K173" s="154">
+        <v>20</v>
+      </c>
+      <c r="L173" s="154">
+        <v>24.857306665477619</v>
+      </c>
+      <c r="M173" s="154">
+        <v>30</v>
+      </c>
+      <c r="N173" s="154">
+        <v>35</v>
+      </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" s="157"/>
@@ -12464,24 +12470,27 @@
       <c r="D174" s="158"/>
       <c r="E174" s="158"/>
       <c r="F174" s="158"/>
-      <c r="I174" s="156">
-        <f>E166</f>
-        <v>5018.3101364638533</v>
-      </c>
-      <c r="J174" s="154">
-        <v>15</v>
-      </c>
-      <c r="K174" s="154">
-        <v>20</v>
-      </c>
-      <c r="L174" s="154">
-        <v>24.857306665477619</v>
-      </c>
-      <c r="M174" s="154">
-        <v>30</v>
-      </c>
-      <c r="N174" s="154">
-        <v>35</v>
+      <c r="H174" s="180" t="s">
+        <v>435</v>
+      </c>
+      <c r="I174" s="153">
+        <v>0.08</v>
+      </c>
+      <c r="J174">
+        <f t="dataTable" ref="J174:N178" dt2D="1" dtr="1" r1="E131" r2="E133" ca="1"/>
+        <v>6257.1179704497345</v>
+      </c>
+      <c r="K174">
+        <v>6768.2011614025869</v>
+      </c>
+      <c r="L174">
+        <v>7264.6987194083604</v>
+      </c>
+      <c r="M174">
+        <v>7790.3675433082944</v>
+      </c>
+      <c r="N174">
+        <v>8301.4507342611469</v>
       </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.3">
@@ -12491,27 +12500,24 @@
       <c r="D175" s="158"/>
       <c r="E175" s="158"/>
       <c r="F175" s="158"/>
-      <c r="H175" s="180" t="s">
-        <v>435</v>
-      </c>
+      <c r="H175" s="180"/>
       <c r="I175" s="153">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="J175">
-        <f t="dataTable" ref="J175:N179" dt2D="1" dtr="1" r1="E131" r2="E133" ca="1"/>
-        <v>6224.3979747805924</v>
-      </c>
-      <c r="K175">
-        <v>6735.4811657334449</v>
-      </c>
-      <c r="L175">
-        <v>7231.9787237392193</v>
-      </c>
-      <c r="M175">
-        <v>7757.6475476391524</v>
+        <v>4827.994618658714</v>
+      </c>
+      <c r="K175" s="159">
+        <v>5320.1562684898654</v>
+      </c>
+      <c r="L175" s="159">
+        <v>5798.2722809333309</v>
+      </c>
+      <c r="M175" s="159">
+        <v>6304.4795681521728</v>
       </c>
       <c r="N175">
-        <v>8268.7307385920049</v>
+        <v>6796.6412179833242</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.3">
@@ -12523,22 +12529,22 @@
       <c r="F176" s="158"/>
       <c r="H176" s="180"/>
       <c r="I176" s="153">
-        <v>0.09</v>
+        <v>9.9840668529013896E-2</v>
       </c>
       <c r="J176">
-        <v>4810.02185888647</v>
+        <v>4093.8361215342584</v>
       </c>
       <c r="K176" s="159">
-        <v>5302.1835087176223</v>
-      </c>
-      <c r="L176" s="159">
-        <v>5780.2995211610878</v>
+        <v>4568.2212553752006</v>
+      </c>
+      <c r="L176" s="160">
+        <v>5029.0680698970209</v>
       </c>
       <c r="M176" s="159">
-        <v>6286.5068083799288</v>
+        <v>5516.991523057085</v>
       </c>
       <c r="N176">
-        <v>6778.668458211082</v>
+        <v>5991.3766568980263</v>
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.3">
@@ -12550,22 +12556,22 @@
       <c r="F177" s="158"/>
       <c r="H177" s="180"/>
       <c r="I177" s="153">
-        <v>9.9840668529013896E-2</v>
+        <v>0.11</v>
       </c>
       <c r="J177">
-        <v>4083.0781881010926</v>
+        <v>3617.2882492127292</v>
       </c>
       <c r="K177" s="159">
-        <v>4557.4633219420348</v>
-      </c>
-      <c r="L177" s="160">
-        <v>5018.3101364638533</v>
+        <v>4074.1515610303195</v>
+      </c>
+      <c r="L177" s="159">
+        <v>4517.9766029710709</v>
       </c>
       <c r="M177" s="159">
-        <v>5506.2335896239183</v>
+        <v>4987.8781846654974</v>
       </c>
       <c r="N177">
-        <v>5980.6187234648614</v>
+        <v>5444.7414964830878</v>
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.3">
@@ -12577,22 +12583,22 @@
       <c r="F178" s="158"/>
       <c r="H178" s="180"/>
       <c r="I178" s="153">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="J178">
-        <v>3610.9430587465386</v>
-      </c>
-      <c r="K178" s="159">
-        <v>4067.8063705641275</v>
-      </c>
-      <c r="L178" s="159">
-        <v>4511.6314125048784</v>
-      </c>
-      <c r="M178" s="159">
-        <v>4981.5329941993077</v>
+        <v>3289.0092053943899</v>
+      </c>
+      <c r="K178">
+        <v>3729.4051205960586</v>
+      </c>
+      <c r="L178">
+        <v>4157.2327234676941</v>
+      </c>
+      <c r="M178">
+        <v>4610.1969509993951</v>
       </c>
       <c r="N178">
-        <v>5438.3963060168971</v>
+        <v>5050.5928662010638</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.3">
@@ -12602,25 +12608,6 @@
       <c r="D179" s="158"/>
       <c r="E179" s="158"/>
       <c r="F179" s="158"/>
-      <c r="H179" s="180"/>
-      <c r="I179" s="153">
-        <v>0.12</v>
-      </c>
-      <c r="J179">
-        <v>3285.5031700616869</v>
-      </c>
-      <c r="K179">
-        <v>3725.8990852633547</v>
-      </c>
-      <c r="L179">
-        <v>4153.7266881349906</v>
-      </c>
-      <c r="M179">
-        <v>4606.6909156666907</v>
-      </c>
-      <c r="N179">
-        <v>5047.0868308683594</v>
-      </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" s="157"/>
@@ -12637,6 +12624,13 @@
       <c r="D181" s="158"/>
       <c r="E181" s="158"/>
       <c r="F181" s="158"/>
+      <c r="J181" s="152" t="s">
+        <v>434</v>
+      </c>
+      <c r="K181" s="151"/>
+      <c r="L181" s="151"/>
+      <c r="M181" s="151"/>
+      <c r="N181" s="151"/>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" s="157"/>
@@ -12645,13 +12639,25 @@
       <c r="D182" s="158"/>
       <c r="E182" s="158"/>
       <c r="F182" s="158"/>
-      <c r="J182" s="152" t="s">
-        <v>434</v>
-      </c>
-      <c r="K182" s="151"/>
-      <c r="L182" s="151"/>
-      <c r="M182" s="151"/>
-      <c r="N182" s="151"/>
+      <c r="I182" s="156">
+        <f>E165</f>
+        <v>5029.0680698970209</v>
+      </c>
+      <c r="J182" s="155">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="K182" s="155">
+        <v>0.05</v>
+      </c>
+      <c r="L182" s="155">
+        <v>0.06</v>
+      </c>
+      <c r="M182" s="155">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="N182" s="155">
+        <v>7.0000000000000007E-2</v>
+      </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" s="157"/>
@@ -12660,24 +12666,27 @@
       <c r="D183" s="158"/>
       <c r="E183" s="158"/>
       <c r="F183" s="158"/>
-      <c r="I183" s="156">
-        <f>E166</f>
-        <v>5018.3101364638533</v>
-      </c>
-      <c r="J183" s="155">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="K183" s="155">
-        <v>0.05</v>
-      </c>
-      <c r="L183" s="155">
-        <v>0.06</v>
-      </c>
-      <c r="M183" s="155">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="N183" s="155">
-        <v>7.0000000000000007E-2</v>
+      <c r="H183" s="180" t="s">
+        <v>435</v>
+      </c>
+      <c r="I183" s="153">
+        <v>0.08</v>
+      </c>
+      <c r="J183">
+        <f t="dataTable" ref="J183:N187" dt2D="1" dtr="1" r1="E132" r2="E133"/>
+        <v>5607.0707557177329</v>
+      </c>
+      <c r="K183">
+        <v>5975.4325254267624</v>
+      </c>
+      <c r="L183">
+        <v>7264.6987194083604</v>
+      </c>
+      <c r="M183">
+        <v>8553.9649133899602</v>
+      </c>
+      <c r="N183">
+        <v>11132.49730135316</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.3">
@@ -12687,27 +12696,24 @@
       <c r="D184" s="158"/>
       <c r="E184" s="158"/>
       <c r="F184" s="158"/>
-      <c r="H184" s="180" t="s">
-        <v>435</v>
-      </c>
+      <c r="H184" s="180"/>
       <c r="I184" s="153">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="J184">
-        <f t="dataTable" ref="J184:N188" dt2D="1" dtr="1" r1="E132" r2="E133"/>
-        <v>5592.4287391101598</v>
-      </c>
-      <c r="K184">
-        <v>5956.77318013884</v>
-      </c>
-      <c r="L184">
-        <v>7231.9787237392193</v>
-      </c>
-      <c r="M184">
-        <v>8507.1842673395986</v>
+        <v>4962.9188695519833</v>
+      </c>
+      <c r="K184" s="159">
+        <v>5171.7572223973211</v>
+      </c>
+      <c r="L184" s="159">
+        <v>5798.2722809333309</v>
+      </c>
+      <c r="M184" s="159">
+        <v>6299.4843277621394</v>
       </c>
       <c r="N184">
-        <v>11057.595354540361</v>
+        <v>7051.3023980053522</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.3">
@@ -12719,22 +12725,22 @@
       <c r="F185" s="158"/>
       <c r="H185" s="180"/>
       <c r="I185" s="153">
-        <v>0.09</v>
+        <v>9.9840668529013896E-2</v>
       </c>
       <c r="J185">
-        <v>4954.0564178891291</v>
+        <v>4527.0709344272573</v>
       </c>
       <c r="K185" s="159">
-        <v>5160.6171937071204</v>
-      </c>
-      <c r="L185" s="159">
-        <v>5780.2995211610878</v>
+        <v>4660.8298510378472</v>
+      </c>
+      <c r="L185" s="160">
+        <v>5029.0680698970209</v>
       </c>
       <c r="M185" s="159">
-        <v>6276.0453831242621</v>
+        <v>5292.4562277704936</v>
       </c>
       <c r="N185">
-        <v>7019.6641760690254</v>
+        <v>5644.1092171162863</v>
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.3">
@@ -12746,22 +12752,22 @@
       <c r="F186" s="158"/>
       <c r="H186" s="180"/>
       <c r="I186" s="153">
-        <v>9.9840668529013896E-2</v>
+        <v>0.11</v>
       </c>
       <c r="J186">
-        <v>4521.7877479836288</v>
+        <v>4189.9601312276354</v>
       </c>
       <c r="K186" s="159">
-        <v>4654.0878988477725</v>
-      </c>
-      <c r="L186" s="160">
-        <v>5018.3101364638533</v>
+        <v>4281.0758178230344</v>
+      </c>
+      <c r="L186" s="159">
+        <v>4517.9766029710709</v>
       </c>
       <c r="M186" s="159">
-        <v>5278.8258008059674</v>
+        <v>4675.9104597364276</v>
       </c>
       <c r="N186">
-        <v>5626.6436863060344</v>
+        <v>4873.3277806931237</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.3">
@@ -12773,22 +12779,22 @@
       <c r="F187" s="158"/>
       <c r="H187" s="180"/>
       <c r="I187" s="153">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="J187">
-        <v>4187.1922663362529</v>
-      </c>
-      <c r="K187" s="159">
-        <v>4277.3142513830944</v>
-      </c>
-      <c r="L187" s="159">
-        <v>4511.6314125048784</v>
-      </c>
-      <c r="M187" s="159">
-        <v>4667.8428532527359</v>
+        <v>3926.8135882073138</v>
+      </c>
+      <c r="K187">
+        <v>3992.6476268531364</v>
+      </c>
+      <c r="L187">
+        <v>4157.2327234676941</v>
+      </c>
+      <c r="M187">
+        <v>4261.9686940405945</v>
       </c>
       <c r="N187">
-        <v>4863.1071541875581</v>
+        <v>4387.6518587280743</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.3">
@@ -12798,39 +12804,12 @@
       <c r="D188" s="158"/>
       <c r="E188" s="158"/>
       <c r="F188" s="158"/>
-      <c r="H188" s="180"/>
-      <c r="I188" s="153">
-        <v>0.12</v>
-      </c>
-      <c r="J188">
-        <v>3925.8204884632128</v>
-      </c>
-      <c r="K188">
-        <v>3990.9365455122925</v>
-      </c>
-      <c r="L188">
-        <v>4153.7266881349906</v>
-      </c>
-      <c r="M188">
-        <v>4257.3204152585258</v>
-      </c>
-      <c r="N188">
-        <v>4381.6328878067679</v>
-      </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A189" s="157"/>
-      <c r="B189" s="157"/>
-      <c r="C189" s="157"/>
-      <c r="D189" s="158"/>
-      <c r="E189" s="158"/>
-      <c r="F189" s="158"/>
-      <c r="H189" s="161"/>
+      <c r="H188" s="161"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="H175:H179"/>
-    <mergeCell ref="H184:H188"/>
+    <mergeCell ref="H174:H178"/>
+    <mergeCell ref="H183:H187"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
